--- a/COSTOS SANITARIOS.xlsx
+++ b/COSTOS SANITARIOS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\KPIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{348723E8-7172-40AC-8889-3931851986DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A5A1F3-913A-4783-B332-3A7E94201895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{339843A6-C640-4B8D-84C5-C4A6EBD4D030}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="25">
   <si>
     <t>ITEM</t>
   </si>
@@ -47,18 +47,9 @@
     <t xml:space="preserve">OT </t>
   </si>
   <si>
-    <t>DETALLES O REQUERIMIENTO</t>
-  </si>
-  <si>
     <t>FECHA</t>
   </si>
   <si>
-    <t>N° SOLIC.</t>
-  </si>
-  <si>
-    <t>N° O.C.</t>
-  </si>
-  <si>
     <t>MONTO</t>
   </si>
   <si>
@@ -105,6 +96,24 @@
   </si>
   <si>
     <t>H Y E</t>
+  </si>
+  <si>
+    <t>SEDE</t>
+  </si>
+  <si>
+    <t>VILLA 2</t>
+  </si>
+  <si>
+    <t>VILLA 1</t>
+  </si>
+  <si>
+    <t>SOLICITUD</t>
+  </si>
+  <si>
+    <t>OC</t>
+  </si>
+  <si>
+    <t>DETALLE</t>
   </si>
 </sst>
 </file>
@@ -114,7 +123,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;S/&quot;\ #,##0.00;[Red]\-&quot;S/&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -129,23 +138,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF36615E"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Verdana"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -153,10 +145,17 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF36615E"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -180,7 +179,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -212,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -221,27 +220,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -578,19 +571,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD6AD95F-99D5-4DE2-9EA6-77D498B4B187}">
-  <dimension ref="A2:I7"/>
+  <dimension ref="A2:J7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="121.85546875" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="17.85546875" customWidth="1"/>
-    <col min="7" max="7" width="25.42578125" customWidth="1"/>
-    <col min="8" max="8" width="49.42578125" customWidth="1"/>
-    <col min="9" max="9" width="23.85546875" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" customWidth="1"/>
+    <col min="5" max="5" width="17.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" customWidth="1"/>
+    <col min="7" max="7" width="17.85546875" customWidth="1"/>
+    <col min="8" max="8" width="25.42578125" customWidth="1"/>
+    <col min="9" max="9" width="49.42578125" customWidth="1"/>
+    <col min="10" max="10" width="23.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -598,166 +592,184 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>155</v>
+      </c>
+      <c r="B3" s="3">
+        <v>80178</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="D3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="5">
+        <v>46147</v>
+      </c>
+      <c r="F3" s="3">
+        <v>32709</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="H3" s="6">
+        <v>9919.67</v>
+      </c>
+      <c r="I3" s="7" t="s">
         <v>8</v>
       </c>
+      <c r="J3" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
-        <v>155</v>
-      </c>
-      <c r="B3" s="4">
-        <v>80178</v>
-      </c>
-      <c r="C3" s="5" t="s">
+    <row r="4" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>172</v>
+      </c>
+      <c r="B4" s="8">
+        <v>81700</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="5">
+        <v>46181</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>176</v>
+      </c>
+      <c r="B5" s="3">
+        <v>81928</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="5">
+        <v>46189</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="6">
+        <v>2171.1999999999998</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="6">
-        <v>46147</v>
-      </c>
-      <c r="E3" s="7">
-        <v>32709</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="8">
-        <v>9919.67</v>
-      </c>
-      <c r="H3" s="9" t="s">
+    </row>
+    <row r="6" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>177</v>
+      </c>
+      <c r="B6" s="3">
+        <v>81930</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="5">
+        <v>46189</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>12</v>
+      <c r="G6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="6">
+        <v>8861.2099999999991</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>172</v>
-      </c>
-      <c r="B4" s="10">
-        <v>81700</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="6">
-        <v>46181</v>
-      </c>
-      <c r="E4" s="4" t="s">
+    <row r="7" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>178</v>
+      </c>
+      <c r="B7" s="3">
+        <v>81933</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="5">
+        <v>46189</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" s="6">
+        <v>4233.84</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
-        <v>176</v>
-      </c>
-      <c r="B5" s="4">
-        <v>81928</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="6">
-        <v>46189</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="8">
-        <v>2171.1999999999998</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
-        <v>177</v>
-      </c>
-      <c r="B6" s="4">
-        <v>81930</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="J7" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="D6" s="6">
-        <v>46189</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="8">
-        <v>8861.2099999999991</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
-        <v>178</v>
-      </c>
-      <c r="B7" s="4">
-        <v>81933</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="6">
-        <v>46189</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="8">
-        <v>4233.84</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/COSTOS SANITARIOS.xlsx
+++ b/COSTOS SANITARIOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\KPIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A5A1F3-913A-4783-B332-3A7E94201895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97928E76-B9D9-4647-A77A-A43B45BB7466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{339843A6-C640-4B8D-84C5-C4A6EBD4D030}"/>
   </bookViews>
@@ -113,7 +113,7 @@
     <t>OC</t>
   </si>
   <si>
-    <t>DETALLE</t>
+    <t>REQUERIMIENTO</t>
   </si>
 </sst>
 </file>
